--- a/output/lgbm_reg/01_feature_analysis/特征分析报告.xlsx
+++ b/output/lgbm_reg/01_feature_analysis/特征分析报告.xlsx
@@ -11,7 +11,6 @@
     <sheet name="by_dataset" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="by_month" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="特征分箱图" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="特征分箱图1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -149,7 +148,7 @@
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -169,12 +168,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>2</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -194,12 +193,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>17</col>
+      <col>3</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -221,10 +220,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -244,12 +243,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -269,12 +268,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>17</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -296,10 +295,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -319,12 +318,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -344,12 +343,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>17</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -371,10 +370,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -394,12 +393,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -419,12 +418,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>17</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>66</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -446,10 +445,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -469,12 +468,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>2</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -494,12 +493,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>17</col>
+      <col>3</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2857500" cy="2095500"/>
+    <ext cx="4572000" cy="3048000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -1271,40 +1270,40 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4967141530112327</v>
+        <v>0.5425600435859647</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004</v>
+        <v>0.0023</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02901000054320895</v>
+        <v>0.1055306776413517</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9837434761835352</v>
+        <v>0.9854939248342827</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.019512155820825</v>
+        <v>-2.696886642941572</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.201848001835626</v>
+        <v>-2.049719958292685</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.564381901623802</v>
+        <v>-1.481812769883007</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6354112519703229</v>
+        <v>-0.5813536610328671</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02129161270400193</v>
+        <v>0.1109225897098661</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6684190677280373</v>
+        <v>0.6703718721105325</v>
       </c>
       <c r="O2" t="n">
-        <v>1.666361214669281</v>
+        <v>1.746223258440527</v>
       </c>
       <c r="P2" t="n">
-        <v>2.339373869568636</v>
+        <v>2.627514695838276</v>
       </c>
       <c r="Q2" t="n">
         <v>3.926237706436327</v>
@@ -1322,44 +1321,44 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0493</v>
+        <v>0.0655</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>0.0493</v>
+        <v>0.0655</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4988037067534395</v>
+        <v>0.5065758242985725</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2865878475351078</v>
+        <v>0.2947500797236264</v>
       </c>
       <c r="I3" t="n">
-        <v>3.071884538241587e-05</v>
+        <v>0.0005979388347953085</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01296042498152146</v>
+        <v>0.0166414449613708</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05456260173924999</v>
+        <v>0.04947116051643035</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2521292135326654</v>
+        <v>0.2488969626780623</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4974366857770134</v>
+        <v>0.5162195990704497</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7452604918035108</v>
+        <v>0.7664657482446764</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9520723282251687</v>
+        <v>0.966701965713764</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9900941777440155</v>
+        <v>0.9921131634873906</v>
       </c>
       <c r="Q3" t="n">
         <v>0.9994606810596731</v>
@@ -1383,43 +1382,43 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3804816888264314</v>
+        <v>-0.1357427633989638</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004</v>
+        <v>0.0023</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.05280446676951486</v>
+        <v>-0.188835980906184</v>
       </c>
       <c r="H4" t="n">
-        <v>2.082422119194164</v>
+        <v>2.110712658443231</v>
       </c>
       <c r="I4" t="n">
-        <v>-7.673311096918739</v>
+        <v>-6.442032711971427</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.769998388669373</v>
+        <v>-5.163720736133728</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.485631726064894</v>
+        <v>-3.89353001357751</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.459066159456222</v>
+        <v>-1.489842024388947</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08158203919324677</v>
+        <v>-0.203973309187356</v>
       </c>
       <c r="N4" t="n">
-        <v>1.384036663511435</v>
+        <v>1.222670788773708</v>
       </c>
       <c r="O4" t="n">
-        <v>3.346023245659287</v>
+        <v>3.272652243614891</v>
       </c>
       <c r="P4" t="n">
-        <v>4.995744074411184</v>
+        <v>4.321024975095314</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.058110375140968</v>
+        <v>6.196598868142515</v>
       </c>
     </row>
     <row r="5">
@@ -1440,40 +1439,40 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6487469372366542</v>
+        <v>0.5112957462460346</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0004</v>
+        <v>0.0023</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4967175363250089</v>
+        <v>0.503737666562812</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2906561817104341</v>
+        <v>0.2933398923906211</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001577445780567288</v>
+        <v>0.005720931541964625</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009850906528665699</v>
+        <v>0.009781718075070016</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0492507227408164</v>
+        <v>0.04807615998030768</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2433527670505238</v>
+        <v>0.2542141271607709</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4855310467246509</v>
+        <v>0.5004948950766138</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7532031361203914</v>
+        <v>0.754653844298574</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9488764775583366</v>
+        <v>0.9619667871924689</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9909893267415298</v>
+        <v>0.9946696237056405</v>
       </c>
       <c r="Q5" t="n">
         <v>0.9996732052420922</v>
@@ -1497,43 +1496,43 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.50831074874755</v>
+        <v>-0.07296943188127829</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0004</v>
+        <v>0.0023</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01696311280962304</v>
+        <v>0.0293737036650229</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9909555892047299</v>
+        <v>0.9111921447614844</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.3755791001776</v>
+        <v>-2.767325422602398</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.314110514290815</v>
+        <v>-2.169781534821386</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.603998183996937</v>
+        <v>-1.426942811289819</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6393356258974371</v>
+        <v>-0.6344775429611836</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0279039485192885</v>
+        <v>0.05338427247902176</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6730848577123615</v>
+        <v>0.617957910056772</v>
       </c>
       <c r="O6" t="n">
-        <v>1.603742908417164</v>
+        <v>1.556028558976306</v>
       </c>
       <c r="P6" t="n">
-        <v>2.379025465955355</v>
+        <v>1.969435505586679</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.428910478008214</v>
+        <v>2.842593728010459</v>
       </c>
     </row>
     <row r="7">
@@ -1554,43 +1553,43 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.030999522495951</v>
+        <v>-0.2341369569491805</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0204</v>
+        <v>0.002</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2738802069516488</v>
+        <v>-0.03639619690860389</v>
       </c>
       <c r="H7" t="n">
-        <v>1.047032327127806</v>
+        <v>0.9894537458204419</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.962625691672579</v>
+        <v>-3.241267340069073</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.683466769183553</v>
+        <v>-2.199653484964395</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.26849156372691</v>
+        <v>-1.584007727269618</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4997301761516306</v>
+        <v>-0.749404003815061</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2685922788632569</v>
+        <v>-0.044509431754544</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8696059201056602</v>
+        <v>0.5802493057773357</v>
       </c>
       <c r="O7" t="n">
-        <v>1.918804264708074</v>
+        <v>1.708665079010738</v>
       </c>
       <c r="P7" t="n">
-        <v>2.584634509105017</v>
+        <v>2.217871937943888</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.949094425308725</v>
+        <v>3.078880808455238</v>
       </c>
     </row>
     <row r="8">
@@ -1605,47 +1604,47 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0612</v>
+        <v>0.0391</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>0.0612</v>
+        <v>0.0391</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4823484782931017</v>
+        <v>0.4987299090043556</v>
       </c>
       <c r="H8" t="n">
-        <v>0.292743315115016</v>
+        <v>0.2901546621501512</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01997293257802812</v>
+        <v>3.071884538241587e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0235135859860793</v>
+        <v>0.006030634807264877</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0407411810894506</v>
+        <v>0.05011467899368909</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2958510804815561</v>
+        <v>0.2455277039181092</v>
       </c>
       <c r="M8" t="n">
-        <v>0.454752044342789</v>
+        <v>0.503619691758018</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7276354575164934</v>
+        <v>0.7563215864211291</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9365235809635636</v>
+        <v>0.9429916084446182</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9855704618363605</v>
+        <v>0.9838752943165207</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9895053333843224</v>
+        <v>0.9987929358156545</v>
       </c>
     </row>
     <row r="9">
@@ -1666,43 +1665,43 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.140628135572932</v>
+        <v>3.177880656888166</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0204</v>
+        <v>0.002</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3557166504910754</v>
+        <v>0.008357916265335625</v>
       </c>
       <c r="H9" t="n">
-        <v>2.047095750802836</v>
+        <v>2.00027988726036</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.303656126089898</v>
+        <v>-4.770227397386073</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.158309242396212</v>
+        <v>-4.118340120585337</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.689985854333752</v>
+        <v>-3.051297653412244</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8566365155955113</v>
+        <v>-1.479576120265062</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06479242736715746</v>
+        <v>-0.1331142284174748</v>
       </c>
       <c r="N9" t="n">
-        <v>1.406285084440008</v>
+        <v>1.396693168642997</v>
       </c>
       <c r="O9" t="n">
-        <v>3.820925717560119</v>
+        <v>3.395714113677164</v>
       </c>
       <c r="P9" t="n">
-        <v>4.306901928189909</v>
+        <v>4.973156296453042</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.508076217842238</v>
+        <v>6.754765838165292</v>
       </c>
     </row>
     <row r="10">
@@ -1723,43 +1722,43 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4705050789923272</v>
+        <v>0.7518762443691909</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0204</v>
+        <v>0.002</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5346369911165936</v>
+        <v>0.4908459758653487</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3071429483961198</v>
+        <v>0.2924537702536322</v>
       </c>
       <c r="I10" t="n">
-        <v>0.003504663531058272</v>
+        <v>0.003929321422217802</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01373090345658189</v>
+        <v>0.008969254814105123</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0559526313833144</v>
+        <v>0.04010607189585737</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2588887419705045</v>
+        <v>0.2292819308092663</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5288052181567664</v>
+        <v>0.4906196847377672</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7922223472439286</v>
+        <v>0.7612842551026815</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9686464453936169</v>
+        <v>0.9304858334143356</v>
       </c>
       <c r="P10" t="n">
-        <v>0.984192400304913</v>
+        <v>0.9729104896739704</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9859719439503437</v>
+        <v>0.9976503383754736</v>
       </c>
     </row>
     <row r="11">
@@ -1780,43 +1779,43 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2587644118723788</v>
+        <v>0.1434289370373244</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0204</v>
+        <v>0.002</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1272071087453728</v>
+        <v>-0.02176318825001877</v>
       </c>
       <c r="H11" t="n">
-        <v>1.149811811125819</v>
+        <v>0.9779025194885634</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.57829285014053</v>
+        <v>-3.3755791001776</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.199438229513767</v>
+        <v>-2.222535137023937</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.667471766770732</v>
+        <v>-1.5535113556854</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5842290931920854</v>
+        <v>-0.6772469280515022</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02050172936766847</v>
+        <v>-0.008388642959532934</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8437900258815756</v>
+        <v>0.6623063309382186</v>
       </c>
       <c r="O11" t="n">
-        <v>1.789917622130343</v>
+        <v>1.566319612056741</v>
       </c>
       <c r="P11" t="n">
-        <v>2.876296555283968</v>
+        <v>2.111004142955458</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.377768241289362</v>
+        <v>3.428910478008214</v>
       </c>
     </row>
     <row r="12">
@@ -1837,43 +1836,43 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4657297535702569</v>
+        <v>0.4967141530112327</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0051</v>
+        <v>0.0005</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01349136405020942</v>
+        <v>0.03319670916850456</v>
       </c>
       <c r="H12" t="n">
-        <v>1.011938226782416</v>
+        <v>0.9857230220589142</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.241267340069073</v>
+        <v>-3.019512155820825</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.624754335424314</v>
+        <v>-2.243079769694367</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.675881557362036</v>
+        <v>-1.579127792039406</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5070981149312093</v>
+        <v>-0.6095122021592831</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02818115736912825</v>
+        <v>0.02246589281204638</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6716709266040162</v>
+        <v>0.6929186230316111</v>
       </c>
       <c r="O12" t="n">
-        <v>1.67681636281563</v>
+        <v>1.642541394632044</v>
       </c>
       <c r="P12" t="n">
-        <v>2.177483467200959</v>
+        <v>2.24313611531757</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.644343347017035</v>
+        <v>3.852731490654721</v>
       </c>
     </row>
     <row r="13">
@@ -1888,47 +1887,47 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0564</v>
+        <v>0.0494</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>0.0564</v>
+        <v>0.0494</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4663323983748345</v>
+        <v>0.4937044220713539</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3046393361911923</v>
+        <v>0.2859358457634777</v>
       </c>
       <c r="I13" t="n">
-        <v>0.005864727887161303</v>
+        <v>0.0002270382182555375</v>
       </c>
       <c r="J13" t="n">
-        <v>0.009007469450112195</v>
+        <v>0.01345372431848352</v>
       </c>
       <c r="K13" t="n">
-        <v>0.03688230533802354</v>
+        <v>0.054663703757422</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1886160963086962</v>
+        <v>0.2508129954686398</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4517374350252467</v>
+        <v>0.4851516824540258</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7286915375963917</v>
+        <v>0.7365535231418538</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9428212045495283</v>
+        <v>0.9470080297040906</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9783135038672698</v>
+        <v>0.9882645756917887</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9859341686249178</v>
+        <v>0.9993503004722002</v>
       </c>
     </row>
     <row r="14">
@@ -1949,43 +1948,43 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.479350936235667</v>
+        <v>-0.3804816888264314</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0051</v>
+        <v>0.0005</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1057281303008786</v>
+        <v>-0.01374421648922313</v>
       </c>
       <c r="H14" t="n">
-        <v>2.058606318821204</v>
+        <v>2.093277023797529</v>
       </c>
       <c r="I14" t="n">
-        <v>-5.415087710762355</v>
+        <v>-7.673311096918739</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.225645573819894</v>
+        <v>-4.76614458288533</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.264098690137281</v>
+        <v>-3.472160541155767</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.284865451291366</v>
+        <v>-1.418862314656952</v>
       </c>
       <c r="M14" t="n">
-        <v>0.03224957580094488</v>
+        <v>-0.024087105919863</v>
       </c>
       <c r="N14" t="n">
-        <v>1.524927497477187</v>
+        <v>1.41882196117321</v>
       </c>
       <c r="O14" t="n">
-        <v>3.440709346818224</v>
+        <v>3.362286884757436</v>
       </c>
       <c r="P14" t="n">
-        <v>4.930484062871603</v>
+        <v>5.032137904837098</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.648440852790406</v>
+        <v>7.058110375140968</v>
       </c>
     </row>
     <row r="15">
@@ -2006,43 +2005,43 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8742965602221743</v>
+        <v>0.6487469372366542</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0051</v>
+        <v>0.0005</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5246792648211624</v>
+        <v>0.5002416984773497</v>
       </c>
       <c r="H15" t="n">
-        <v>0.292586559703757</v>
+        <v>0.2903371826791601</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001203613909017909</v>
+        <v>0.0001577445780567288</v>
       </c>
       <c r="J15" t="n">
-        <v>0.00435917262650501</v>
+        <v>0.009153607848917965</v>
       </c>
       <c r="K15" t="n">
-        <v>0.06068884477495479</v>
+        <v>0.0536421498850342</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2548327827965651</v>
+        <v>0.2453104979859799</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5300884969144239</v>
+        <v>0.4885611605848416</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8074541179457937</v>
+        <v>0.7553389295039722</v>
       </c>
       <c r="O15" t="n">
-        <v>0.968240851934323</v>
+        <v>0.9532694247456598</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9882851716576241</v>
+        <v>0.9901557068242997</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9901917892516717</v>
+        <v>0.9993351228311154</v>
       </c>
     </row>
     <row r="16">
@@ -2063,43 +2062,43 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9413814861392652</v>
+        <v>1.50831074874755</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0051</v>
+        <v>0.0005</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.07993078670888254</v>
+        <v>0.01737270683814999</v>
       </c>
       <c r="H16" t="n">
-        <v>1.044832658665467</v>
+        <v>1.020000335520404</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.946904219284014</v>
+        <v>-3.321114555589139</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.494253714238831</v>
+        <v>-2.363257941455723</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.625334325045426</v>
+        <v>-1.672318115008392</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7630617056336235</v>
+        <v>-0.6448958586443377</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1450336915284224</v>
+        <v>0.01742895295810179</v>
       </c>
       <c r="N16" t="n">
-        <v>0.594034747895963</v>
+        <v>0.6875507195924941</v>
       </c>
       <c r="O16" t="n">
-        <v>1.654524102872334</v>
+        <v>1.656166746018412</v>
       </c>
       <c r="P16" t="n">
-        <v>2.330839747794095</v>
+        <v>2.447347323787493</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.186574911811055</v>
+        <v>3.377768241289362</v>
       </c>
     </row>
   </sheetData>
@@ -30340,57 +30339,50 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R61"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="68.57142857142857" customWidth="1" min="2" max="2"/>
+    <col width="68.57142857142857" customWidth="1" min="3" max="3"/>
+    <col width="68.57142857142857" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="426.6666666666667" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="23" ht="426.6666666666667" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>f2</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="45" ht="426.6666666666667" customHeight="1">
+      <c r="A45" t="inlineStr">
         <is>
           <t>f3</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="67" ht="426.6666666666667" customHeight="1">
+      <c r="A67" t="inlineStr">
         <is>
           <t>f4</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="89" ht="426.6666666666667" customHeight="1">
+      <c r="A89" t="inlineStr">
         <is>
           <t>f5</t>
         </is>
